--- a/SHET/GZRPN001/gzrpnc1.xlsx
+++ b/SHET/GZRPN001/gzrpnc1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WWWW\protocols\SHET\GZRPN001\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC198CC-B5C0-4A57-9293-544D836B09AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155F4811-64D7-4896-B160-9BE30C0D7FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,9 +55,6 @@
     <t>X:161, X:221</t>
   </si>
   <si>
-    <t>Срабатывание выходного реле при введеном SA1</t>
-  </si>
-  <si>
     <t>Сброс блокировки ГЗ,ТЗ</t>
   </si>
   <si>
@@ -98,6 +95,9 @@
   </si>
   <si>
     <t>ГЗ РПН: Блокировка ф.С</t>
+  </si>
+  <si>
+    <t>Срабатывание выходного реле</t>
   </si>
 </sst>
 </file>
@@ -434,13 +434,13 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>2</v>
@@ -468,13 +468,13 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>4</v>
@@ -494,10 +494,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>4</v>
@@ -517,10 +517,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>4</v>
@@ -540,10 +540,10 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>4</v>
@@ -560,13 +560,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>4</v>
@@ -583,13 +583,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>4</v>
@@ -606,13 +606,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>4</v>
@@ -629,10 +629,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>7</v>
@@ -675,7 +675,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -683,7 +683,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
